--- a/artfynd/A 21849-2024 artfynd.xlsx
+++ b/artfynd/A 21849-2024 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001286</v>
+        <v>118001285</v>
       </c>
       <c r="B9" t="n">
-        <v>74584</v>
+        <v>98170</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448235</v>
+        <v>448255</v>
       </c>
       <c r="R9" t="n">
-        <v>7033072</v>
+        <v>7033054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001279</v>
+        <v>118001286</v>
       </c>
       <c r="B10" t="n">
-        <v>90464</v>
+        <v>74584</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,25 +1597,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448261</v>
+        <v>448235</v>
       </c>
       <c r="R10" t="n">
-        <v>7033059</v>
+        <v>7033072</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001242</v>
+        <v>118001279</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>90464</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,25 +1709,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448236</v>
+        <v>448261</v>
       </c>
       <c r="R11" t="n">
-        <v>7033106</v>
+        <v>7033059</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001285</v>
+        <v>118001242</v>
       </c>
       <c r="B12" t="n">
-        <v>98170</v>
+        <v>78480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,25 +1821,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448255</v>
+        <v>448236</v>
       </c>
       <c r="R12" t="n">
-        <v>7033054</v>
+        <v>7033106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001264</v>
+        <v>118001256</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448319</v>
+        <v>448181</v>
       </c>
       <c r="R13" t="n">
-        <v>7033288</v>
+        <v>7033202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001256</v>
+        <v>118001264</v>
       </c>
       <c r="B14" t="n">
-        <v>97753</v>
+        <v>78480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448181</v>
+        <v>448319</v>
       </c>
       <c r="R14" t="n">
-        <v>7033202</v>
+        <v>7033288</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001257</v>
+        <v>118001276</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>82259</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448181</v>
+        <v>448273</v>
       </c>
       <c r="R15" t="n">
-        <v>7033203</v>
+        <v>7033079</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001276</v>
+        <v>118001257</v>
       </c>
       <c r="B16" t="n">
-        <v>82259</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,21 +2273,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448273</v>
+        <v>448181</v>
       </c>
       <c r="R16" t="n">
-        <v>7033079</v>
+        <v>7033203</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2705,7 +2705,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001249</v>
+        <v>118001273</v>
       </c>
       <c r="B20" t="n">
         <v>79597</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448232</v>
+        <v>448309</v>
       </c>
       <c r="R20" t="n">
-        <v>7033143</v>
+        <v>7033158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001273</v>
+        <v>118001249</v>
       </c>
       <c r="B21" t="n">
         <v>79597</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448309</v>
+        <v>448232</v>
       </c>
       <c r="R21" t="n">
-        <v>7033158</v>
+        <v>7033143</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001266</v>
+        <v>118001283</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>82259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,21 +3281,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448295</v>
+        <v>448253</v>
       </c>
       <c r="R25" t="n">
-        <v>7033242</v>
+        <v>7033058</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001261</v>
+        <v>118001274</v>
       </c>
       <c r="B26" t="n">
-        <v>97753</v>
+        <v>74583</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,38 +3389,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448270</v>
+        <v>448287</v>
       </c>
       <c r="R26" t="n">
-        <v>7033292</v>
+        <v>7033136</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3465,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,8 +3474,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3489,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001283</v>
+        <v>118001252</v>
       </c>
       <c r="B27" t="n">
-        <v>82259</v>
+        <v>79590</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,25 +3520,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,10 +3548,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448253</v>
+        <v>448187</v>
       </c>
       <c r="R27" t="n">
-        <v>7033058</v>
+        <v>7033158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,7 +3583,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3593,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001274</v>
+        <v>118001266</v>
       </c>
       <c r="B28" t="n">
-        <v>74583</v>
+        <v>78480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3613,41 +3632,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448287</v>
+        <v>448295</v>
       </c>
       <c r="R28" t="n">
-        <v>7033136</v>
+        <v>7033242</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,7 +3695,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3705,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,24 +3714,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001252</v>
+        <v>118001261</v>
       </c>
       <c r="B29" t="n">
-        <v>79590</v>
+        <v>97753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3748,21 +3748,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448187</v>
+        <v>448270</v>
       </c>
       <c r="R29" t="n">
-        <v>7033158</v>
+        <v>7033292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001241</v>
+        <v>118001259</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3856,25 +3856,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448170</v>
+        <v>448179</v>
       </c>
       <c r="R30" t="n">
-        <v>7033072</v>
+        <v>7033243</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4068,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001259</v>
+        <v>118001241</v>
       </c>
       <c r="B32" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448179</v>
+        <v>448170</v>
       </c>
       <c r="R32" t="n">
-        <v>7033243</v>
+        <v>7033072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5315,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001246</v>
+        <v>118001255</v>
       </c>
       <c r="B43" t="n">
-        <v>74592</v>
+        <v>97857</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,25 +5327,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448228</v>
+        <v>448181</v>
       </c>
       <c r="R43" t="n">
-        <v>7033188</v>
+        <v>7033202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001255</v>
+        <v>118001246</v>
       </c>
       <c r="B44" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448181</v>
+        <v>448228</v>
       </c>
       <c r="R44" t="n">
-        <v>7033202</v>
+        <v>7033188</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 21849-2024 artfynd.xlsx
+++ b/artfynd/A 21849-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118001253</v>
+        <v>118001286</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>74584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448178</v>
+        <v>448235</v>
       </c>
       <c r="R2" t="n">
-        <v>7033175</v>
+        <v>7033072</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118001268</v>
+        <v>118001261</v>
       </c>
       <c r="B3" t="n">
-        <v>57440</v>
+        <v>97753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448320</v>
+        <v>448270</v>
       </c>
       <c r="R3" t="n">
-        <v>7033178</v>
+        <v>7033292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001250</v>
+        <v>118001277</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>97740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448209</v>
+        <v>448267</v>
       </c>
       <c r="R4" t="n">
-        <v>7033109</v>
+        <v>7033061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001272</v>
+        <v>118001290</v>
       </c>
       <c r="B5" t="n">
-        <v>74592</v>
+        <v>79562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448310</v>
+        <v>448232</v>
       </c>
       <c r="R5" t="n">
-        <v>7033159</v>
+        <v>7033068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001254</v>
+        <v>118001257</v>
       </c>
       <c r="B6" t="n">
-        <v>104914</v>
+        <v>78480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448176</v>
+        <v>448181</v>
       </c>
       <c r="R6" t="n">
-        <v>7033164</v>
+        <v>7033203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001280</v>
+        <v>118001291</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448259</v>
+        <v>448219</v>
       </c>
       <c r="R7" t="n">
-        <v>7033071</v>
+        <v>7033069</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001248</v>
+        <v>118001274</v>
       </c>
       <c r="B8" t="n">
-        <v>74592</v>
+        <v>74583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,38 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448250</v>
+        <v>448287</v>
       </c>
       <c r="R8" t="n">
-        <v>7033163</v>
+        <v>7033136</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,8 +1444,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001285</v>
+        <v>118001250</v>
       </c>
       <c r="B9" t="n">
-        <v>98170</v>
+        <v>78480</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448255</v>
+        <v>448209</v>
       </c>
       <c r="R9" t="n">
-        <v>7033054</v>
+        <v>7033109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001286</v>
+        <v>118001263</v>
       </c>
       <c r="B10" t="n">
-        <v>74584</v>
+        <v>79590</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448235</v>
+        <v>448291</v>
       </c>
       <c r="R10" t="n">
-        <v>7033072</v>
+        <v>7033295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001279</v>
+        <v>118001253</v>
       </c>
       <c r="B11" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448261</v>
+        <v>448178</v>
       </c>
       <c r="R11" t="n">
-        <v>7033059</v>
+        <v>7033175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001242</v>
+        <v>118001264</v>
       </c>
       <c r="B12" t="n">
         <v>78480</v>
@@ -1849,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448236</v>
+        <v>448319</v>
       </c>
       <c r="R12" t="n">
-        <v>7033106</v>
+        <v>7033288</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001256</v>
+        <v>118001279</v>
       </c>
       <c r="B13" t="n">
-        <v>97753</v>
+        <v>90464</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448181</v>
+        <v>448261</v>
       </c>
       <c r="R13" t="n">
-        <v>7033202</v>
+        <v>7033059</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001264</v>
+        <v>118001265</v>
       </c>
       <c r="B14" t="n">
-        <v>78480</v>
+        <v>74584</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,21 +2054,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2073,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448319</v>
+        <v>448279</v>
       </c>
       <c r="R14" t="n">
-        <v>7033288</v>
+        <v>7033281</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001276</v>
+        <v>118001241</v>
       </c>
       <c r="B15" t="n">
-        <v>82259</v>
+        <v>78480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2166,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448273</v>
+        <v>448170</v>
       </c>
       <c r="R15" t="n">
-        <v>7033079</v>
+        <v>7033072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2235,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001257</v>
+        <v>118001255</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,25 +2274,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,7 +2305,7 @@
         <v>448181</v>
       </c>
       <c r="R16" t="n">
-        <v>7033203</v>
+        <v>7033202</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2347,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001265</v>
+        <v>118001288</v>
       </c>
       <c r="B17" t="n">
-        <v>74584</v>
+        <v>74576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,25 +2386,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448279</v>
+        <v>448235</v>
       </c>
       <c r="R17" t="n">
-        <v>7033281</v>
+        <v>7033071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2449,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2459,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,7 +2486,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001247</v>
+        <v>118001266</v>
       </c>
       <c r="B18" t="n">
         <v>78480</v>
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448250</v>
+        <v>448295</v>
       </c>
       <c r="R18" t="n">
-        <v>7033163</v>
+        <v>7033242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2571,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001294</v>
+        <v>118001267</v>
       </c>
       <c r="B19" t="n">
-        <v>74592</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,21 +2614,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448215</v>
+        <v>448284</v>
       </c>
       <c r="R19" t="n">
-        <v>7033027</v>
+        <v>7033201</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2673,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2683,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001273</v>
+        <v>118001247</v>
       </c>
       <c r="B20" t="n">
-        <v>79597</v>
+        <v>78480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,25 +2722,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2750,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448309</v>
+        <v>448250</v>
       </c>
       <c r="R20" t="n">
-        <v>7033158</v>
+        <v>7033163</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001249</v>
+        <v>118001289</v>
       </c>
       <c r="B21" t="n">
-        <v>79597</v>
+        <v>79590</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448232</v>
+        <v>448231</v>
       </c>
       <c r="R21" t="n">
-        <v>7033143</v>
+        <v>7033068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2907,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001277</v>
+        <v>118001262</v>
       </c>
       <c r="B22" t="n">
-        <v>97740</v>
+        <v>97753</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,21 +2950,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2974,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448267</v>
+        <v>448279</v>
       </c>
       <c r="R22" t="n">
-        <v>7033061</v>
+        <v>7033291</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3004,7 +3009,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3019,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001291</v>
+        <v>118001283</v>
       </c>
       <c r="B23" t="n">
-        <v>97857</v>
+        <v>82259</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,25 +3058,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448219</v>
+        <v>448253</v>
       </c>
       <c r="R23" t="n">
-        <v>7033069</v>
+        <v>7033058</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3116,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001271</v>
+        <v>118001243</v>
       </c>
       <c r="B24" t="n">
-        <v>77417</v>
+        <v>79562</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448310</v>
+        <v>448269</v>
       </c>
       <c r="R24" t="n">
-        <v>7033159</v>
+        <v>7033132</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001283</v>
+        <v>118001258</v>
       </c>
       <c r="B25" t="n">
-        <v>82259</v>
+        <v>57287</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,34 +3286,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448253</v>
+        <v>448169</v>
       </c>
       <c r="R25" t="n">
-        <v>7033058</v>
+        <v>7033250</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,7 +3350,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3360,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001274</v>
+        <v>118001276</v>
       </c>
       <c r="B26" t="n">
-        <v>74583</v>
+        <v>82259</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,41 +3404,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448287</v>
+        <v>448273</v>
       </c>
       <c r="R26" t="n">
-        <v>7033136</v>
+        <v>7033079</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3467,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3477,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,24 +3486,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3508,10 +3504,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001252</v>
+        <v>118001270</v>
       </c>
       <c r="B27" t="n">
-        <v>79590</v>
+        <v>82259</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3520,25 +3516,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3548,10 +3544,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448187</v>
+        <v>448310</v>
       </c>
       <c r="R27" t="n">
-        <v>7033158</v>
+        <v>7033161</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,7 +3579,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3589,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3620,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001266</v>
+        <v>118001293</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>77417</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3636,21 +3632,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3660,10 +3656,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448295</v>
+        <v>448217</v>
       </c>
       <c r="R28" t="n">
-        <v>7033242</v>
+        <v>7033026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3695,7 +3691,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3705,7 +3701,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3732,10 +3728,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001261</v>
+        <v>118001273</v>
       </c>
       <c r="B29" t="n">
-        <v>97753</v>
+        <v>79597</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3748,21 +3744,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3772,10 +3768,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448270</v>
+        <v>448309</v>
       </c>
       <c r="R29" t="n">
-        <v>7033292</v>
+        <v>7033158</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3807,7 +3803,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3817,7 +3813,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3844,10 +3840,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001259</v>
+        <v>118001272</v>
       </c>
       <c r="B30" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3856,25 +3852,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3884,10 +3880,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448179</v>
+        <v>448310</v>
       </c>
       <c r="R30" t="n">
-        <v>7033243</v>
+        <v>7033159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3919,7 +3915,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,7 +3925,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,10 +3952,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001263</v>
+        <v>118001292</v>
       </c>
       <c r="B31" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,25 +3964,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3996,10 +3992,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448291</v>
+        <v>448216</v>
       </c>
       <c r="R31" t="n">
-        <v>7033295</v>
+        <v>7033042</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,7 +4027,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,7 +4037,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4068,10 +4064,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001241</v>
+        <v>118001281</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,21 +4080,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4104,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448170</v>
+        <v>448249</v>
       </c>
       <c r="R32" t="n">
-        <v>7033072</v>
+        <v>7033073</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4143,7 +4139,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,7 +4149,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4164,6 +4160,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4180,10 +4191,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001262</v>
+        <v>118001285</v>
       </c>
       <c r="B33" t="n">
-        <v>97753</v>
+        <v>98170</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4196,21 +4207,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4220,10 +4231,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448279</v>
+        <v>448255</v>
       </c>
       <c r="R33" t="n">
-        <v>7033291</v>
+        <v>7033054</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4255,7 +4266,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,7 +4276,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,10 +4303,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001267</v>
+        <v>118001256</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4315,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4343,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448284</v>
+        <v>448181</v>
       </c>
       <c r="R34" t="n">
-        <v>7033201</v>
+        <v>7033202</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,7 +4378,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4377,7 +4388,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4415,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001288</v>
+        <v>118001254</v>
       </c>
       <c r="B35" t="n">
-        <v>74576</v>
+        <v>104914</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4420,21 +4431,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4444,10 +4455,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448235</v>
+        <v>448176</v>
       </c>
       <c r="R35" t="n">
-        <v>7033071</v>
+        <v>7033164</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,7 +4490,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4489,7 +4500,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4516,10 +4527,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001243</v>
+        <v>118001245</v>
       </c>
       <c r="B36" t="n">
-        <v>79562</v>
+        <v>78480</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,21 +4543,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4556,10 +4567,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448269</v>
+        <v>448229</v>
       </c>
       <c r="R36" t="n">
-        <v>7033132</v>
+        <v>7033197</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,7 +4602,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4601,7 +4612,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4639,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001269</v>
+        <v>118001248</v>
       </c>
       <c r="B37" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4640,25 +4651,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4668,10 +4679,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448320</v>
+        <v>448250</v>
       </c>
       <c r="R37" t="n">
-        <v>7033180</v>
+        <v>7033163</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4703,7 +4714,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4713,7 +4724,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4740,10 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001292</v>
+        <v>118001252</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4752,25 +4763,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4780,10 +4791,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448216</v>
+        <v>448187</v>
       </c>
       <c r="R38" t="n">
-        <v>7033042</v>
+        <v>7033158</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4815,7 +4826,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4825,7 +4836,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,10 +4863,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001290</v>
+        <v>118001246</v>
       </c>
       <c r="B39" t="n">
-        <v>79562</v>
+        <v>74592</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4868,21 +4879,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4892,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448232</v>
+        <v>448228</v>
       </c>
       <c r="R39" t="n">
-        <v>7033068</v>
+        <v>7033188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4927,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4937,7 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4964,10 +4975,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001289</v>
+        <v>118001242</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4976,25 +4987,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5004,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448231</v>
+        <v>448236</v>
       </c>
       <c r="R40" t="n">
-        <v>7033068</v>
+        <v>7033106</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5039,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5049,7 +5060,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5076,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001281</v>
+        <v>118001294</v>
       </c>
       <c r="B41" t="n">
-        <v>79562</v>
+        <v>74592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,21 +5103,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5116,10 +5127,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448249</v>
+        <v>448215</v>
       </c>
       <c r="R41" t="n">
-        <v>7033073</v>
+        <v>7033027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5151,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5161,7 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5172,21 +5183,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5203,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001270</v>
+        <v>118001259</v>
       </c>
       <c r="B42" t="n">
-        <v>82259</v>
+        <v>97857</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5215,25 +5211,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5243,10 +5239,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448310</v>
+        <v>448179</v>
       </c>
       <c r="R42" t="n">
-        <v>7033161</v>
+        <v>7033243</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5278,7 +5274,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5288,7 +5284,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,7 +5311,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001255</v>
+        <v>118001269</v>
       </c>
       <c r="B43" t="n">
         <v>97857</v>
@@ -5355,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448181</v>
+        <v>448320</v>
       </c>
       <c r="R43" t="n">
-        <v>7033202</v>
+        <v>7033180</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5390,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5400,7 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5427,10 +5423,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001246</v>
+        <v>118001249</v>
       </c>
       <c r="B44" t="n">
-        <v>74592</v>
+        <v>79597</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5439,25 +5435,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448228</v>
+        <v>448232</v>
       </c>
       <c r="R44" t="n">
-        <v>7033188</v>
+        <v>7033143</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5502,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5512,7 +5508,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5539,10 +5535,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001258</v>
+        <v>118001244</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5555,39 +5551,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448169</v>
+        <v>448270</v>
       </c>
       <c r="R45" t="n">
-        <v>7033250</v>
+        <v>7033133</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5619,7 +5610,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5629,12 +5620,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5661,10 +5647,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001293</v>
+        <v>118001260</v>
       </c>
       <c r="B46" t="n">
-        <v>77417</v>
+        <v>78480</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5677,21 +5663,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5701,10 +5687,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448217</v>
+        <v>448214</v>
       </c>
       <c r="R46" t="n">
-        <v>7033026</v>
+        <v>7033242</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5736,7 +5722,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5746,7 +5732,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5773,7 +5759,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001260</v>
+        <v>118001275</v>
       </c>
       <c r="B47" t="n">
         <v>78480</v>
@@ -5813,10 +5799,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448214</v>
+        <v>448288</v>
       </c>
       <c r="R47" t="n">
-        <v>7033242</v>
+        <v>7033123</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5848,7 +5834,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5844,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5885,7 +5871,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001275</v>
+        <v>118001280</v>
       </c>
       <c r="B48" t="n">
         <v>78480</v>
@@ -5925,10 +5911,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448288</v>
+        <v>448259</v>
       </c>
       <c r="R48" t="n">
-        <v>7033123</v>
+        <v>7033071</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5960,7 +5946,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5970,7 +5956,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5997,10 +5983,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001245</v>
+        <v>118001271</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>77417</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6013,21 +5999,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6037,10 +6023,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448229</v>
+        <v>448310</v>
       </c>
       <c r="R49" t="n">
-        <v>7033197</v>
+        <v>7033159</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6072,7 +6058,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6082,7 +6068,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6109,10 +6095,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001244</v>
+        <v>118001268</v>
       </c>
       <c r="B50" t="n">
-        <v>79561</v>
+        <v>57440</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6125,34 +6111,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448270</v>
+        <v>448320</v>
       </c>
       <c r="R50" t="n">
-        <v>7033133</v>
+        <v>7033178</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6184,7 +6179,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6194,7 +6189,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 21849-2024 artfynd.xlsx
+++ b/artfynd/A 21849-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118001286</v>
+        <v>118001257</v>
       </c>
       <c r="B2" t="n">
-        <v>74584</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448235</v>
+        <v>448181</v>
       </c>
       <c r="R2" t="n">
-        <v>7033072</v>
+        <v>7033203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118001261</v>
+        <v>118001291</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>97859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448270</v>
+        <v>448219</v>
       </c>
       <c r="R3" t="n">
-        <v>7033292</v>
+        <v>7033069</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001277</v>
+        <v>118001286</v>
       </c>
       <c r="B4" t="n">
-        <v>97740</v>
+        <v>74586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448267</v>
+        <v>448235</v>
       </c>
       <c r="R4" t="n">
-        <v>7033061</v>
+        <v>7033072</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001290</v>
+        <v>118001277</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>97742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448232</v>
+        <v>448267</v>
       </c>
       <c r="R5" t="n">
-        <v>7033068</v>
+        <v>7033061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001257</v>
+        <v>118001273</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>79599</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448181</v>
+        <v>448309</v>
       </c>
       <c r="R6" t="n">
-        <v>7033203</v>
+        <v>7033158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001291</v>
+        <v>118001263</v>
       </c>
       <c r="B7" t="n">
-        <v>97857</v>
+        <v>79592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448219</v>
+        <v>448291</v>
       </c>
       <c r="R7" t="n">
-        <v>7033069</v>
+        <v>7033295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001274</v>
+        <v>118001272</v>
       </c>
       <c r="B8" t="n">
-        <v>74583</v>
+        <v>74594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,41 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448287</v>
+        <v>448310</v>
       </c>
       <c r="R8" t="n">
-        <v>7033136</v>
+        <v>7033159</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,24 +1441,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1478,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001250</v>
+        <v>118001271</v>
       </c>
       <c r="B9" t="n">
-        <v>78480</v>
+        <v>77419</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448209</v>
+        <v>448310</v>
       </c>
       <c r="R9" t="n">
-        <v>7033109</v>
+        <v>7033159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001263</v>
+        <v>118001292</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448291</v>
+        <v>448216</v>
       </c>
       <c r="R10" t="n">
-        <v>7033295</v>
+        <v>7033042</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001253</v>
+        <v>118001288</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>74578</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448178</v>
+        <v>448235</v>
       </c>
       <c r="R11" t="n">
-        <v>7033175</v>
+        <v>7033071</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001264</v>
+        <v>118001275</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448319</v>
+        <v>448288</v>
       </c>
       <c r="R12" t="n">
-        <v>7033288</v>
+        <v>7033123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001279</v>
+        <v>118001280</v>
       </c>
       <c r="B13" t="n">
-        <v>90464</v>
+        <v>78482</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448261</v>
+        <v>448259</v>
       </c>
       <c r="R13" t="n">
-        <v>7033059</v>
+        <v>7033071</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001265</v>
+        <v>118001256</v>
       </c>
       <c r="B14" t="n">
-        <v>74584</v>
+        <v>97755</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448279</v>
+        <v>448181</v>
       </c>
       <c r="R14" t="n">
-        <v>7033281</v>
+        <v>7033202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001241</v>
+        <v>118001261</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2190,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448170</v>
+        <v>448270</v>
       </c>
       <c r="R15" t="n">
-        <v>7033072</v>
+        <v>7033292</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001255</v>
+        <v>118001254</v>
       </c>
       <c r="B16" t="n">
-        <v>97857</v>
+        <v>104916</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448181</v>
+        <v>448176</v>
       </c>
       <c r="R16" t="n">
-        <v>7033202</v>
+        <v>7033164</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2347,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001288</v>
+        <v>118001289</v>
       </c>
       <c r="B17" t="n">
-        <v>74576</v>
+        <v>79592</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2414,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448235</v>
+        <v>448231</v>
       </c>
       <c r="R17" t="n">
-        <v>7033071</v>
+        <v>7033068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2449,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001266</v>
+        <v>118001250</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448295</v>
+        <v>448209</v>
       </c>
       <c r="R18" t="n">
-        <v>7033242</v>
+        <v>7033109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,7 +2582,7 @@
         <v>118001267</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2710,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001247</v>
+        <v>118001264</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448250</v>
+        <v>448319</v>
       </c>
       <c r="R20" t="n">
-        <v>7033163</v>
+        <v>7033288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001289</v>
+        <v>118001245</v>
       </c>
       <c r="B21" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448231</v>
+        <v>448229</v>
       </c>
       <c r="R21" t="n">
-        <v>7033068</v>
+        <v>7033197</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2907,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001262</v>
+        <v>118001248</v>
       </c>
       <c r="B22" t="n">
-        <v>97753</v>
+        <v>74594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2974,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448279</v>
+        <v>448250</v>
       </c>
       <c r="R22" t="n">
-        <v>7033291</v>
+        <v>7033163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3019,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001283</v>
+        <v>118001252</v>
       </c>
       <c r="B23" t="n">
-        <v>82259</v>
+        <v>79592</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448253</v>
+        <v>448187</v>
       </c>
       <c r="R23" t="n">
-        <v>7033058</v>
+        <v>7033158</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001243</v>
+        <v>118001262</v>
       </c>
       <c r="B24" t="n">
-        <v>79562</v>
+        <v>97755</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448269</v>
+        <v>448279</v>
       </c>
       <c r="R24" t="n">
-        <v>7033132</v>
+        <v>7033291</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001258</v>
+        <v>118001243</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>79564</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,39 +3267,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448169</v>
+        <v>448269</v>
       </c>
       <c r="R25" t="n">
-        <v>7033250</v>
+        <v>7033132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3350,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,12 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001276</v>
+        <v>118001265</v>
       </c>
       <c r="B26" t="n">
-        <v>82259</v>
+        <v>74586</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3432,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448273</v>
+        <v>448279</v>
       </c>
       <c r="R26" t="n">
-        <v>7033079</v>
+        <v>7033281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3467,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3477,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001270</v>
+        <v>118001242</v>
       </c>
       <c r="B27" t="n">
-        <v>82259</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3520,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3544,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448310</v>
+        <v>448236</v>
       </c>
       <c r="R27" t="n">
-        <v>7033161</v>
+        <v>7033106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3589,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3616,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001293</v>
+        <v>118001274</v>
       </c>
       <c r="B28" t="n">
-        <v>77417</v>
+        <v>74585</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3628,38 +3599,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448217</v>
+        <v>448287</v>
       </c>
       <c r="R28" t="n">
-        <v>7033026</v>
+        <v>7033136</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3691,7 +3665,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3701,7 +3675,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,8 +3684,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Vid basen av sälgstubbe, i skrymslen på den avfallande barken samt på hymeniet av död ticka. # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3728,10 +3718,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001273</v>
+        <v>118001255</v>
       </c>
       <c r="B29" t="n">
-        <v>79597</v>
+        <v>97859</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3744,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3768,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448309</v>
+        <v>448181</v>
       </c>
       <c r="R29" t="n">
-        <v>7033158</v>
+        <v>7033202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3803,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3813,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,10 +3830,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001272</v>
+        <v>118001246</v>
       </c>
       <c r="B30" t="n">
-        <v>74592</v>
+        <v>74594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,10 +3870,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448310</v>
+        <v>448228</v>
       </c>
       <c r="R30" t="n">
-        <v>7033159</v>
+        <v>7033188</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3915,7 +3905,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3925,7 +3915,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,10 +3942,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001292</v>
+        <v>118001270</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>82261</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,21 +3958,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3992,10 +3982,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448216</v>
+        <v>448310</v>
       </c>
       <c r="R31" t="n">
-        <v>7033042</v>
+        <v>7033161</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4027,7 +4017,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4037,7 +4027,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,10 +4054,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001281</v>
+        <v>118001293</v>
       </c>
       <c r="B32" t="n">
-        <v>79562</v>
+        <v>77419</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,21 +4070,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4104,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448249</v>
+        <v>448217</v>
       </c>
       <c r="R32" t="n">
-        <v>7033073</v>
+        <v>7033026</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,7 +4129,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4149,7 +4139,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,21 +4150,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4191,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001285</v>
+        <v>118001260</v>
       </c>
       <c r="B33" t="n">
-        <v>98170</v>
+        <v>78482</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4203,25 +4178,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4231,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>448255</v>
+        <v>448214</v>
       </c>
       <c r="R33" t="n">
-        <v>7033054</v>
+        <v>7033242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4266,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4276,7 +4251,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4303,10 +4278,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001256</v>
+        <v>118001279</v>
       </c>
       <c r="B34" t="n">
-        <v>97753</v>
+        <v>90466</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4319,21 +4294,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4343,10 +4318,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448181</v>
+        <v>448261</v>
       </c>
       <c r="R34" t="n">
-        <v>7033202</v>
+        <v>7033059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4378,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4388,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4415,10 +4390,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001254</v>
+        <v>118001290</v>
       </c>
       <c r="B35" t="n">
-        <v>104914</v>
+        <v>79564</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4427,25 +4402,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4455,10 +4430,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448176</v>
+        <v>448232</v>
       </c>
       <c r="R35" t="n">
-        <v>7033164</v>
+        <v>7033068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4490,7 +4465,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4500,7 +4475,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4527,10 +4502,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001245</v>
+        <v>118001268</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>57441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4543,34 +4518,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448229</v>
+        <v>448320</v>
       </c>
       <c r="R36" t="n">
-        <v>7033197</v>
+        <v>7033178</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4602,7 +4586,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4612,7 +4596,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4639,10 +4628,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001248</v>
+        <v>118001285</v>
       </c>
       <c r="B37" t="n">
-        <v>74592</v>
+        <v>98172</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4651,25 +4640,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>219880</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4679,10 +4668,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448250</v>
+        <v>448255</v>
       </c>
       <c r="R37" t="n">
-        <v>7033163</v>
+        <v>7033054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4714,7 +4703,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4724,7 +4713,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4751,10 +4740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001252</v>
+        <v>118001249</v>
       </c>
       <c r="B38" t="n">
-        <v>79590</v>
+        <v>79599</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4767,21 +4756,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4791,10 +4780,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>448187</v>
+        <v>448232</v>
       </c>
       <c r="R38" t="n">
-        <v>7033158</v>
+        <v>7033143</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4826,7 +4815,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4836,7 +4825,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001246</v>
+        <v>118001247</v>
       </c>
       <c r="B39" t="n">
-        <v>74592</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4879,21 +4868,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4903,10 +4892,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448228</v>
+        <v>448250</v>
       </c>
       <c r="R39" t="n">
-        <v>7033188</v>
+        <v>7033163</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4938,7 +4927,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,7 +4937,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001242</v>
+        <v>118001253</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5015,10 +5004,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448236</v>
+        <v>448178</v>
       </c>
       <c r="R40" t="n">
-        <v>7033106</v>
+        <v>7033175</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5050,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,7 +5049,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001294</v>
+        <v>118001283</v>
       </c>
       <c r="B41" t="n">
-        <v>74592</v>
+        <v>82261</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5103,21 +5092,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5127,10 +5116,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448215</v>
+        <v>448253</v>
       </c>
       <c r="R41" t="n">
-        <v>7033027</v>
+        <v>7033058</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,7 +5161,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001259</v>
+        <v>118001281</v>
       </c>
       <c r="B42" t="n">
-        <v>97857</v>
+        <v>79564</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5211,25 +5200,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5239,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>448179</v>
+        <v>448249</v>
       </c>
       <c r="R42" t="n">
-        <v>7033243</v>
+        <v>7033073</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5274,7 +5263,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5284,7 +5273,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5295,6 +5284,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5311,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001269</v>
+        <v>118001244</v>
       </c>
       <c r="B43" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5323,25 +5327,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5351,10 +5355,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448320</v>
+        <v>448270</v>
       </c>
       <c r="R43" t="n">
-        <v>7033180</v>
+        <v>7033133</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,7 +5390,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5396,7 +5400,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5423,10 +5427,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001249</v>
+        <v>118001276</v>
       </c>
       <c r="B44" t="n">
-        <v>79597</v>
+        <v>82261</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5435,25 +5439,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448232</v>
+        <v>448273</v>
       </c>
       <c r="R44" t="n">
-        <v>7033143</v>
+        <v>7033079</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,7 +5502,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5508,7 +5512,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5535,10 +5539,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001244</v>
+        <v>118001241</v>
       </c>
       <c r="B45" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,21 +5555,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5575,10 +5579,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448270</v>
+        <v>448170</v>
       </c>
       <c r="R45" t="n">
-        <v>7033133</v>
+        <v>7033072</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5610,7 +5614,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5620,7 +5624,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001260</v>
+        <v>118001259</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5659,25 +5663,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5687,10 +5691,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448214</v>
+        <v>448179</v>
       </c>
       <c r="R46" t="n">
-        <v>7033242</v>
+        <v>7033243</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5722,7 +5726,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5759,10 +5763,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001275</v>
+        <v>118001269</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5771,25 +5775,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5799,10 +5803,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448288</v>
+        <v>448320</v>
       </c>
       <c r="R47" t="n">
-        <v>7033123</v>
+        <v>7033180</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5834,7 +5838,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5844,7 +5848,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5871,10 +5875,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001280</v>
+        <v>118001266</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5911,10 +5915,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>448259</v>
+        <v>448295</v>
       </c>
       <c r="R48" t="n">
-        <v>7033071</v>
+        <v>7033242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5946,7 +5950,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5956,7 +5960,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5983,10 +5987,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001271</v>
+        <v>118001294</v>
       </c>
       <c r="B49" t="n">
-        <v>77417</v>
+        <v>74594</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5999,21 +6003,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6023,10 +6027,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448310</v>
+        <v>448215</v>
       </c>
       <c r="R49" t="n">
-        <v>7033159</v>
+        <v>7033027</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6058,7 +6062,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6068,7 +6072,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6095,10 +6099,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001268</v>
+        <v>118001258</v>
       </c>
       <c r="B50" t="n">
-        <v>57440</v>
+        <v>57288</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6111,31 +6115,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>448320</v>
+        <v>448169</v>
       </c>
       <c r="R50" t="n">
-        <v>7033178</v>
+        <v>7033250</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 21849-2024 artfynd.xlsx
+++ b/artfynd/A 21849-2024 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001292</v>
+        <v>118001256</v>
       </c>
       <c r="B10" t="n">
-        <v>78482</v>
+        <v>97755</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448216</v>
+        <v>448181</v>
       </c>
       <c r="R10" t="n">
-        <v>7033042</v>
+        <v>7033202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001288</v>
+        <v>118001261</v>
       </c>
       <c r="B11" t="n">
-        <v>74578</v>
+        <v>97755</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448235</v>
+        <v>448270</v>
       </c>
       <c r="R11" t="n">
-        <v>7033071</v>
+        <v>7033292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001275</v>
+        <v>118001254</v>
       </c>
       <c r="B12" t="n">
-        <v>78482</v>
+        <v>104916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448288</v>
+        <v>448176</v>
       </c>
       <c r="R12" t="n">
-        <v>7033123</v>
+        <v>7033164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001280</v>
+        <v>118001292</v>
       </c>
       <c r="B13" t="n">
         <v>78482</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448259</v>
+        <v>448216</v>
       </c>
       <c r="R13" t="n">
-        <v>7033071</v>
+        <v>7033042</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001256</v>
+        <v>118001288</v>
       </c>
       <c r="B14" t="n">
-        <v>97755</v>
+        <v>74578</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448181</v>
+        <v>448235</v>
       </c>
       <c r="R14" t="n">
-        <v>7033202</v>
+        <v>7033071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001261</v>
+        <v>118001275</v>
       </c>
       <c r="B15" t="n">
-        <v>97755</v>
+        <v>78482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448270</v>
+        <v>448288</v>
       </c>
       <c r="R15" t="n">
-        <v>7033292</v>
+        <v>7033123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001254</v>
+        <v>118001280</v>
       </c>
       <c r="B16" t="n">
-        <v>104916</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448176</v>
+        <v>448259</v>
       </c>
       <c r="R16" t="n">
-        <v>7033164</v>
+        <v>7033071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001268</v>
+        <v>118001285</v>
       </c>
       <c r="B36" t="n">
-        <v>57441</v>
+        <v>98172</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4514,47 +4514,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448320</v>
+        <v>448255</v>
       </c>
       <c r="R36" t="n">
-        <v>7033178</v>
+        <v>7033054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,7 +4577,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4596,12 +4587,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001285</v>
+        <v>118001268</v>
       </c>
       <c r="B37" t="n">
-        <v>98172</v>
+        <v>57441</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4640,38 +4626,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Öretjärnen S, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448255</v>
+        <v>448320</v>
       </c>
       <c r="R37" t="n">
-        <v>7033054</v>
+        <v>7033178</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4703,7 +4698,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4713,7 +4708,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Min antal. Vuxna med tiggande, flygga ungar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5427,10 +5427,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001276</v>
+        <v>118001269</v>
       </c>
       <c r="B44" t="n">
-        <v>82261</v>
+        <v>97859</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5439,25 +5439,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448273</v>
+        <v>448320</v>
       </c>
       <c r="R44" t="n">
-        <v>7033079</v>
+        <v>7033180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5539,10 +5539,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001241</v>
+        <v>118001259</v>
       </c>
       <c r="B45" t="n">
-        <v>78482</v>
+        <v>97859</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5551,25 +5551,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448170</v>
+        <v>448179</v>
       </c>
       <c r="R45" t="n">
-        <v>7033072</v>
+        <v>7033243</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001259</v>
+        <v>118001276</v>
       </c>
       <c r="B46" t="n">
-        <v>97859</v>
+        <v>82261</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5663,25 +5663,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448179</v>
+        <v>448273</v>
       </c>
       <c r="R46" t="n">
-        <v>7033243</v>
+        <v>7033079</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5763,10 +5763,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001269</v>
+        <v>118001241</v>
       </c>
       <c r="B47" t="n">
-        <v>97859</v>
+        <v>78482</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5775,25 +5775,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>448320</v>
+        <v>448170</v>
       </c>
       <c r="R47" t="n">
-        <v>7033180</v>
+        <v>7033072</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
